--- a/Windows_Ransomware_Intrusion/evidence/EventLogs/Security.xlsx
+++ b/Windows_Ransomware_Intrusion/evidence/EventLogs/Security.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emma\Desktop\evidence\System\Event Logs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emma/DFIR-Simulation-Platform/Windows_Ransomware_Intrusion/evidence/EventLogs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52925B44-9A97-47C2-9CF0-9EE007DBE156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156ECDF2-F7C7-1145-A1F3-C9AE98111339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="15324" windowHeight="12336" xr2:uid="{B5ED4C35-E770-453D-8C8A-A91827AEEDDF}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="21500" windowHeight="16540" xr2:uid="{B5ED4C35-E770-453D-8C8A-A91827AEEDDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Security" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="60">
   <si>
     <t>TimeCreated</t>
   </si>
@@ -2500,6 +2500,54 @@
 Process Information:
 	Process ID:		0x2cc
 	Process Name:		C:\Windows\System32\winlogon.exe
+Network Information:
+	Workstation Name:	-
+	Source Network Address:	-
+	Source Port:		-
+Detailed Authentication Information:
+	Logon Process:		Advapi  
+	Authentication Package:	Negotiate
+	Transited Services:	-
+	Package Name (NTLM only):	-
+	Key Length:		0
+This event is generated when a logon session is created. It is generated on the computer that was accessed.
+The subject fields indicate the account on the local system which requested the logon. This is most commonly a service such as the Server service, or a local process such as Winlogon.exe or Services.exe.
+The logon type field indicates the kind of logon that occurred. The most common types are 2 (interactive) and 3 (network).
+The New Logon fields indicate the account for whom the new logon was created, i.e. the account that was logged on.
+The network fields indicate where a remote logon request originated. Workstation name is not always available and may be left blank in some cases.
+The impersonation level field indicates the extent to which a process in the logon session can impersonate.
+The authentication information fields provide detailed information about this specific logon request.
+	- Logon GUID is a unique identifier that can be used to correlate this event with a KDC event.
+	- Transited services indicate which intermediate services have participated in this logon request.
+	- Package name indicates which sub-protocol was used among the NTLM protocols.
+	- Key length indicates the length of the generated session key. This will be 0 if no session key was requested.</t>
+  </si>
+  <si>
+    <t>An account was successfully logged on.
+Subject:
+	Security ID:		S-1-5-18
+	Account Name:		SE-PC-MTANNER$
+	Account Domain:		WORKGROUP
+	Logon ID:		0x3E7
+Logon Information:
+	Logon Type:		5
+	Restricted Admin Mode:	-
+	Remote Credential Guard:	-
+	Virtual Account:		No
+	Elevated Token:		Yes
+Impersonation Level:		Impersonation
+New Logon:
+	Security ID:		S-1-5-18
+	Account Name:		SYSTEM
+	Account Domain:		NT AUTHORITY
+	Logon ID:		0x3E7
+	Linked Logon ID:		0x0
+	Network Account Name:	-
+	Network Account Domain:	-
+	Logon GUID:		{00000000-0000-0000-0000-000000000000}
+Process Information:
+	Process ID:		0x314
+	Process Name:		C:\Windows\System32\services.exe
 Network Information:
 	Workstation Name:	-
 	Source Network Address:	-
@@ -3060,7 +3108,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3409,15 +3457,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4DB692-B7D1-489B-A6A7-2F7F64737DB0}">
   <dimension ref="A1:D230"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="97.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="160.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3431,7 +3479,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3442,10 +3490,10 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3456,10 +3504,10 @@
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3473,7 +3521,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3487,7 +3535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3501,7 +3549,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3515,7 +3563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3529,7 +3577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3543,7 +3591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3557,7 +3605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3571,7 +3619,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3585,7 +3633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3599,7 +3647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3613,7 +3661,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3627,7 +3675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3641,7 +3689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3655,7 +3703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3669,7 +3717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3683,7 +3731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3697,7 +3745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3711,7 +3759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3725,7 +3773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3739,7 +3787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3753,7 +3801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3767,7 +3815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3781,7 +3829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3795,7 +3843,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3809,7 +3857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3823,7 +3871,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3837,7 +3885,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3851,7 +3899,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3865,7 +3913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3879,7 +3927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3893,7 +3941,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3907,7 +3955,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3921,7 +3969,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3935,7 +3983,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3949,7 +3997,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3963,7 +4011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3977,7 +4025,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -3991,7 +4039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -4005,7 +4053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -4019,7 +4067,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -4033,7 +4081,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -4047,7 +4095,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -4061,7 +4109,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -4075,7 +4123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -4089,7 +4137,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>46136.751388888886</v>
       </c>
@@ -4103,7 +4151,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4117,7 +4165,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4131,7 +4179,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4145,7 +4193,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4159,7 +4207,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4173,7 +4221,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4187,7 +4235,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4201,7 +4249,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="176" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4215,7 +4263,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" ht="176" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4229,7 +4277,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" ht="272" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4243,7 +4291,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4257,7 +4305,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4271,7 +4319,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" ht="272" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4285,7 +4333,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4299,7 +4347,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4313,7 +4361,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4327,7 +4375,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4341,7 +4389,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4355,7 +4403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4369,7 +4417,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4383,7 +4431,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4397,7 +4445,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4411,7 +4459,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4425,7 +4473,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4439,7 +4487,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4453,7 +4501,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4467,7 +4515,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4481,7 +4529,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4495,7 +4543,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4509,7 +4557,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4523,7 +4571,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4537,7 +4585,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4551,7 +4599,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4565,7 +4613,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4579,7 +4627,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4593,7 +4641,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4607,7 +4655,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4621,7 +4669,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4635,7 +4683,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4649,7 +4697,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4663,7 +4711,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4677,7 +4725,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4691,7 +4739,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4705,7 +4753,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4719,7 +4767,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4733,7 +4781,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4747,7 +4795,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4761,7 +4809,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4775,7 +4823,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4789,7 +4837,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4803,7 +4851,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4817,7 +4865,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4831,7 +4879,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4845,7 +4893,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4859,7 +4907,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4873,7 +4921,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4887,7 +4935,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>46136.752083333333</v>
       </c>
@@ -4901,7 +4949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>46136.75277777778</v>
       </c>
@@ -4915,7 +4963,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>46136.75277777778</v>
       </c>
@@ -4929,7 +4977,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>46136.75277777778</v>
       </c>
@@ -4943,7 +4991,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>46136.75277777778</v>
       </c>
@@ -4957,7 +5005,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>46136.753472222219</v>
       </c>
@@ -4971,7 +5019,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>46136.753472222219</v>
       </c>
@@ -4985,7 +5033,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>46136.753472222219</v>
       </c>
@@ -4999,7 +5047,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>46136.753472222219</v>
       </c>
@@ -5013,7 +5061,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>46136.753472222219</v>
       </c>
@@ -5027,7 +5075,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>46136.753472222219</v>
       </c>
@@ -5041,7 +5089,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>46136.754861111112</v>
       </c>
@@ -5055,7 +5103,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>46136.754861111112</v>
       </c>
@@ -5069,7 +5117,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>46136.758333333331</v>
       </c>
@@ -5083,7 +5131,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>46136.759027777778</v>
       </c>
@@ -5097,7 +5145,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>46136.759722222225</v>
       </c>
@@ -5111,7 +5159,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>46136.761805555558</v>
       </c>
@@ -5125,7 +5173,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>46136.762499999997</v>
       </c>
@@ -5139,7 +5187,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>46136.762499999997</v>
       </c>
@@ -5153,7 +5201,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>46136.772222222222</v>
       </c>
@@ -5167,7 +5215,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>46136.772916666669</v>
       </c>
@@ -5181,7 +5229,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>46136.772916666669</v>
       </c>
@@ -5195,7 +5243,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>46136.773611111108</v>
       </c>
@@ -5209,7 +5257,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>46136.773611111108</v>
       </c>
@@ -5223,7 +5271,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>46136.773611111108</v>
       </c>
@@ -5237,7 +5285,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>46136.773611111108</v>
       </c>
@@ -5251,7 +5299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>46136.773611111108</v>
       </c>
@@ -5265,7 +5313,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5279,7 +5327,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5293,7 +5341,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5307,7 +5355,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" ht="272" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5321,7 +5369,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5335,7 +5383,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5349,7 +5397,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5363,7 +5411,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5377,7 +5425,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5391,7 +5439,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5405,7 +5453,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5419,7 +5467,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5433,7 +5481,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5447,7 +5495,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" ht="272" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5461,7 +5509,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" ht="272" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5475,7 +5523,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" ht="176" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5489,7 +5537,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5503,7 +5551,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" ht="272" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5517,7 +5565,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" ht="272" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>46136.776388888888</v>
       </c>
@@ -5531,7 +5579,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>46136.777083333334</v>
       </c>
@@ -5545,7 +5593,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>46136.777083333334</v>
       </c>
@@ -5559,7 +5607,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>46136.777083333334</v>
       </c>
@@ -5573,7 +5621,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>46136.777083333334</v>
       </c>
@@ -5587,7 +5635,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>46136.779166666667</v>
       </c>
@@ -5601,7 +5649,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>46136.779166666667</v>
       </c>
@@ -5615,7 +5663,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>46136.78125</v>
       </c>
@@ -5629,7 +5677,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" ht="144" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>46136.783333333333</v>
       </c>
@@ -5643,7 +5691,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>46136.783333333333</v>
       </c>
@@ -5657,7 +5705,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" ht="176" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>46136.783333333333</v>
       </c>
@@ -5671,7 +5719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>46136.783333333333</v>
       </c>
@@ -5685,7 +5733,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" ht="144" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>46136.783333333333</v>
       </c>
@@ -5699,7 +5747,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>46136.783333333333</v>
       </c>
@@ -5713,7 +5761,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5727,7 +5775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5741,7 +5789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5755,7 +5803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5769,7 +5817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5783,7 +5831,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5797,7 +5845,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5811,7 +5859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5825,7 +5873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5839,7 +5887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5853,7 +5901,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5867,7 +5915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5881,7 +5929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5895,7 +5943,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5909,7 +5957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5923,7 +5971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5937,7 +5985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5951,7 +5999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5965,7 +6013,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5979,7 +6027,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -5993,7 +6041,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -6007,7 +6055,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -6021,7 +6069,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -6035,7 +6083,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -6049,7 +6097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -6063,7 +6111,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>46136.78402777778</v>
       </c>
@@ -6077,7 +6125,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6091,7 +6139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6105,7 +6153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6119,7 +6167,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6133,7 +6181,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6147,7 +6195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6161,7 +6209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6175,7 +6223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6189,7 +6237,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6203,7 +6251,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6217,7 +6265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6231,7 +6279,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" ht="176" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6245,7 +6293,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="203" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" ht="176" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6259,7 +6307,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" ht="272" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6273,7 +6321,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6287,7 +6335,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6301,7 +6349,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" ht="272" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6315,7 +6363,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6329,7 +6377,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6343,7 +6391,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6357,7 +6405,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6371,7 +6419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6385,7 +6433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6399,7 +6447,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6413,7 +6461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6427,7 +6475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6441,7 +6489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6455,7 +6503,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6469,7 +6517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6483,7 +6531,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>46136.784722222219</v>
       </c>
@@ -6497,7 +6545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>46136.785416666666</v>
       </c>
@@ -6511,7 +6559,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>46136.785416666666</v>
       </c>
@@ -6525,7 +6573,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>46136.785416666666</v>
       </c>
@@ -6539,7 +6587,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>46136.786111111112</v>
       </c>
@@ -6553,7 +6601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>46136.786111111112</v>
       </c>
@@ -6567,7 +6615,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>46136.786111111112</v>
       </c>
@@ -6581,7 +6629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>46136.786111111112</v>
       </c>
@@ -6595,7 +6643,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>46136.786111111112</v>
       </c>
@@ -6609,7 +6657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>46136.787499999999</v>
       </c>
@@ -6623,7 +6671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" ht="144" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>46136.787499999999</v>
       </c>
